--- a/resource/groundTruths/CF_M05_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M05_ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26A46F6-DB7F-C147-97DB-EBB0A25A84B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA3EA46-8DD1-9048-AA62-85A1609B7C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{314DEFDA-1C02-5241-A4B3-474CF73BD97A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="72">
   <si>
     <t>Document ID</t>
   </si>
@@ -92,12 +92,6 @@
   </si>
   <si>
     <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-  </si>
-  <si>
-    <t>CF_M05_R05</t>
-  </si>
-  <si>
-    <t>Ensure that other customers' data cannot be accessed.</t>
   </si>
   <si>
     <t>CF_M05_R06</t>
@@ -246,41 +240,29 @@
     <t>15a. Access</t>
   </si>
   <si>
-    <t>CF_M05_R23</t>
-  </si>
-  <si>
-    <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
-  </si>
-  <si>
-    <t>CF_M01_R24</t>
-  </si>
-  <si>
     <t>The application must manage a strict separation of data for each customer.</t>
   </si>
   <si>
     <t>15b. Integrity</t>
   </si>
   <si>
-    <t>CF_M05_R25</t>
-  </si>
-  <si>
-    <t>No user can access data from other customers.</t>
+    <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
   </si>
   <si>
     <t>CF_M05_R24</t>
   </si>
   <si>
-    <t>CF_M05_R26</t>
-  </si>
-  <si>
-    <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
+    <t>Ensure that other customers' data cannot be accessed.</t>
+  </si>
+  <si>
+    <t>CF_M01_R23</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -317,6 +299,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -764,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55F0498-975D-5543-B4DE-A2F011D05D83}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -881,35 +870,35 @@
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8">
         <v>49</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>12</v>
@@ -927,10 +916,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>12</v>
@@ -948,19 +937,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8">
@@ -973,18 +962,18 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H10" s="5">
         <v>52</v>
@@ -996,19 +985,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8">
@@ -1021,18 +1010,18 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H12" s="5">
         <v>53</v>
@@ -1044,19 +1033,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8">
@@ -1069,18 +1058,18 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H14" s="5">
         <v>53</v>
@@ -1092,19 +1081,19 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8">
@@ -1117,18 +1106,18 @@
         <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H16" s="5">
         <v>53</v>
@@ -1140,19 +1129,19 @@
         <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8">
@@ -1165,18 +1154,18 @@
         <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H18" s="5">
         <v>53</v>
@@ -1188,19 +1177,19 @@
         <v>9</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8">
@@ -1213,18 +1202,18 @@
         <v>9</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H20" s="5">
         <v>54</v>
@@ -1236,19 +1225,19 @@
         <v>9</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8">
@@ -1261,18 +1250,18 @@
         <v>9</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H22" s="5">
         <v>54</v>
@@ -1284,19 +1273,19 @@
         <v>9</v>
       </c>
       <c r="B23" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="F23" s="15" t="s">
         <v>27</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>29</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="16">
@@ -1305,99 +1294,54 @@
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8">
+        <v>55</v>
+      </c>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" s="5">
-        <v>54</v>
-      </c>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8">
-        <v>55</v>
-      </c>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="5">
-        <v>55</v>
-      </c>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="17" t="s">
+      <c r="D25" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17">
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17">
         <v>59</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D27" xr:uid="{28A6E1B6-5A79-2D48-9CD4-D586AB0CD0B2}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D25" xr:uid="{28A6E1B6-5A79-2D48-9CD4-D586AB0CD0B2}">
       <formula1>"FR,QR,Constraint,Criterion"</formula1>
     </dataValidation>
   </dataValidations>

--- a/resource/groundTruths/CF_M05_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M05_ground_truth.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA3EA46-8DD1-9048-AA62-85A1609B7C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F2ED24-4B24-9143-9B0E-F7F2C4403209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{314DEFDA-1C02-5241-A4B3-474CF73BD97A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
   <si>
     <t>Document ID</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>Criterion</t>
-  </si>
-  <si>
-    <t>CF_M01_R08</t>
   </si>
   <si>
     <t>CF_M05_R10</t>
@@ -179,9 +176,6 @@
     <t>Learning time for new features should not exceed 5 min.</t>
   </si>
   <si>
-    <t>CF_M01_R14</t>
-  </si>
-  <si>
     <t>CF_M05_R16</t>
   </si>
   <si>
@@ -255,7 +249,10 @@
     <t>Ensure that other customers' data cannot be accessed.</t>
   </si>
   <si>
-    <t>CF_M01_R23</t>
+    <t>CF_M05_R23</t>
+  </si>
+  <si>
+    <t>CF_M05_R05</t>
   </si>
 </sst>
 </file>
@@ -874,10 +871,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>12</v>
@@ -973,7 +970,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H10" s="5">
         <v>52</v>
@@ -985,16 +982,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>27</v>
@@ -1010,10 +1007,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>30</v>
@@ -1021,7 +1018,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H12" s="5">
         <v>53</v>
@@ -1033,16 +1030,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>27</v>
@@ -1058,10 +1055,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>30</v>
@@ -1069,7 +1066,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H14" s="5">
         <v>53</v>
@@ -1081,16 +1078,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>27</v>
@@ -1106,10 +1103,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>30</v>
@@ -1117,7 +1114,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H16" s="5">
         <v>53</v>
@@ -1129,16 +1126,16 @@
         <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>27</v>
@@ -1154,10 +1151,10 @@
         <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>30</v>
@@ -1165,7 +1162,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H18" s="5">
         <v>53</v>
@@ -1177,16 +1174,16 @@
         <v>9</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>27</v>
@@ -1202,10 +1199,10 @@
         <v>9</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>30</v>
@@ -1213,7 +1210,7 @@
       <c r="E20" s="13"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H20" s="5">
         <v>54</v>
@@ -1225,16 +1222,16 @@
         <v>9</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>27</v>
@@ -1250,10 +1247,10 @@
         <v>9</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>30</v>
@@ -1261,7 +1258,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H22" s="5">
         <v>54</v>
@@ -1273,16 +1270,16 @@
         <v>9</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>27</v>
@@ -1298,16 +1295,16 @@
         <v>9</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>27</v>
@@ -1323,10 +1320,10 @@
         <v>9</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>12</v>
